--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maiten Izquierdo\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E26CC4D-0415-4DEC-877A-D3F14863B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="6825" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jugadores" sheetId="4" r:id="rId1"/>
@@ -21,17 +22,26 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Equipo!$A$1:$C$73</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="68">
   <si>
     <t>Fecha</t>
   </si>
@@ -240,7 +250,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -553,7 +563,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -816,7 +826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1010,8 +1020,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C73"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1820,15 +1830,147 @@
         <v>67</v>
       </c>
     </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C73"/>
+  <autoFilter ref="A1:C73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D74"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2870,14 +3012,182 @@
         <v>0</v>
       </c>
     </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>47</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>52</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3023,6 +3333,28 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45771</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maiten Izquierdo\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E26CC4D-0415-4DEC-877A-D3F14863B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5689411A-A53A-43F3-81D1-4B7CF29C838E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="68">
   <si>
     <t>Fecha</t>
   </si>
@@ -1021,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1960,6 +1960,138 @@
       </c>
       <c r="C85" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -3180,6 +3312,174 @@
         <v>2</v>
       </c>
     </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>51</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3187,7 +3487,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,6 +3655,28 @@
         <v>6</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45785</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maiten Izquierdo\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5689411A-A53A-43F3-81D1-4B7CF29C838E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD76BDA-90B6-44D9-996F-693B39425E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="70">
   <si>
     <t>Fecha</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>Sebas</t>
+  </si>
+  <si>
+    <t>Juan Brancos</t>
+  </si>
+  <si>
+    <t>Maxi</t>
   </si>
 </sst>
 </file>
@@ -564,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -818,6 +824,11 @@
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2092,6 +2103,138 @@
       </c>
       <c r="C97" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2245,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -3480,6 +3623,188 @@
         <v>1</v>
       </c>
     </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>48</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>54</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>69</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>51</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3487,7 +3812,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3677,6 +4002,28 @@
         <v>7</v>
       </c>
     </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45799</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maiten Izquierdo\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD76BDA-90B6-44D9-996F-693B39425E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0731C93F-C179-4758-8864-F912A7E6C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="73">
   <si>
     <t>Fecha</t>
   </si>
@@ -251,6 +251,15 @@
   </si>
   <si>
     <t>Maxi</t>
+  </si>
+  <si>
+    <t>Mati (primo Bigo)</t>
+  </si>
+  <si>
+    <t>Mudito</t>
+  </si>
+  <si>
+    <t>Clota</t>
   </si>
 </sst>
 </file>
@@ -570,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -829,6 +838,21 @@
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1032,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2235,6 +2259,138 @@
       </c>
       <c r="C109" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2245,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -3805,6 +3961,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>70</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>69</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>35</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>71</v>
+      </c>
+      <c r="D118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>72</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>57</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
+        <v>33</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3812,7 +4136,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4024,6 +4348,28 @@
         <v>4</v>
       </c>
     </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45806</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maiten Izquierdo\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0731C93F-C179-4758-8864-F912A7E6C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F153FB9-84FA-4640-AFBE-FF26EA692A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="76">
   <si>
     <t>Fecha</t>
   </si>
@@ -260,6 +260,15 @@
   </si>
   <si>
     <t>Clota</t>
+  </si>
+  <si>
+    <t>Javi</t>
+  </si>
+  <si>
+    <t>Tano</t>
+  </si>
+  <si>
+    <t>Hakimi</t>
   </si>
 </sst>
 </file>
@@ -579,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -853,6 +862,21 @@
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2391,6 +2415,270 @@
       </c>
       <c r="C121" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2401,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -4129,6 +4417,342 @@
         <v>0</v>
       </c>
     </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>33</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>43</v>
+      </c>
+      <c r="D126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
+        <v>73</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>57</v>
+      </c>
+      <c r="D129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>16</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B133" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B134" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" t="s">
+        <v>74</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B135" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" t="s">
+        <v>75</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>57</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
+        <v>51</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>47</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B144" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" t="s">
+        <v>30</v>
+      </c>
+      <c r="D144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" t="s">
+        <v>75</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>65</v>
+      </c>
+      <c r="D147">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4136,7 +4760,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4370,6 +4994,50 @@
         <v>3</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45813</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45820</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\JuevesdelCorderoSusurrador\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="186" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F66EBB44-384C-4D0A-B157-D805CD792392}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jugadores" sheetId="4" r:id="rId1"/>
@@ -21,9 +22,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Equipo!$A$1:$C$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Goles!$A$1:$D$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Goles!$A$1:$D$403</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,6 +36,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="87">
   <si>
     <t>Fecha</t>
   </si>
@@ -298,11 +301,17 @@
   <si>
     <t>Roja</t>
   </si>
+  <si>
+    <t>Amigo Pata</t>
+  </si>
+  <si>
+    <t>Chicho</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -344,10 +353,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -629,16 +637,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -649,7 +657,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -660,7 +668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -671,7 +679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -682,7 +690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -693,7 +701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -704,7 +712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -715,7 +723,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -726,7 +734,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -737,7 +745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -748,7 +756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -759,7 +767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -770,7 +778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -781,7 +789,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -792,7 +800,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -803,7 +811,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -814,7 +822,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -825,12 +833,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -838,7 +846,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -849,7 +857,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -860,7 +868,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -868,7 +876,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -876,52 +884,52 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>76</v>
       </c>
@@ -932,11 +940,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -947,7 +955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -958,7 +966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -969,7 +977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -980,7 +988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -991,7 +999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1002,7 +1010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1013,7 +1021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1024,7 +1032,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1035,7 +1043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1046,7 +1054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1057,7 +1065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1068,7 +1076,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1079,7 +1087,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -1090,7 +1098,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1101,7 +1109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -1109,7 +1117,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1126,14 +1134,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45722</v>
       </c>
@@ -1155,7 +1163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45722</v>
       </c>
@@ -1166,7 +1174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45722</v>
       </c>
@@ -1177,7 +1185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45722</v>
       </c>
@@ -1188,7 +1196,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45722</v>
       </c>
@@ -1199,7 +1207,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45722</v>
       </c>
@@ -1210,7 +1218,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45722</v>
       </c>
@@ -1221,7 +1229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45722</v>
       </c>
@@ -1232,7 +1240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45722</v>
       </c>
@@ -1243,7 +1251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45722</v>
       </c>
@@ -1254,7 +1262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45722</v>
       </c>
@@ -1265,7 +1273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45722</v>
       </c>
@@ -1276,7 +1284,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45729</v>
       </c>
@@ -1287,7 +1295,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45729</v>
       </c>
@@ -1298,7 +1306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45729</v>
       </c>
@@ -1309,7 +1317,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45729</v>
       </c>
@@ -1320,7 +1328,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45729</v>
       </c>
@@ -1331,7 +1339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45729</v>
       </c>
@@ -1342,7 +1350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45729</v>
       </c>
@@ -1353,7 +1361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45729</v>
       </c>
@@ -1364,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45729</v>
       </c>
@@ -1375,7 +1383,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45729</v>
       </c>
@@ -1386,7 +1394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45729</v>
       </c>
@@ -1397,7 +1405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45729</v>
       </c>
@@ -1408,7 +1416,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45736</v>
       </c>
@@ -1419,7 +1427,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45736</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45736</v>
       </c>
@@ -1441,7 +1449,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45736</v>
       </c>
@@ -1452,7 +1460,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45736</v>
       </c>
@@ -1463,7 +1471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45736</v>
       </c>
@@ -1474,7 +1482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45736</v>
       </c>
@@ -1485,7 +1493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45736</v>
       </c>
@@ -1496,7 +1504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45736</v>
       </c>
@@ -1507,7 +1515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45736</v>
       </c>
@@ -1518,7 +1526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45736</v>
       </c>
@@ -1529,7 +1537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45736</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45743</v>
       </c>
@@ -1551,7 +1559,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45743</v>
       </c>
@@ -1562,7 +1570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45743</v>
       </c>
@@ -1573,7 +1581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45743</v>
       </c>
@@ -1584,7 +1592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45743</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45743</v>
       </c>
@@ -1606,7 +1614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45743</v>
       </c>
@@ -1617,7 +1625,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45743</v>
       </c>
@@ -1628,7 +1636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45743</v>
       </c>
@@ -1639,7 +1647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45743</v>
       </c>
@@ -1650,7 +1658,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45743</v>
       </c>
@@ -1661,7 +1669,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45743</v>
       </c>
@@ -1672,7 +1680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45750</v>
       </c>
@@ -1683,7 +1691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45750</v>
       </c>
@@ -1694,7 +1702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45750</v>
       </c>
@@ -1705,7 +1713,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45750</v>
       </c>
@@ -1716,7 +1724,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45750</v>
       </c>
@@ -1727,7 +1735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45750</v>
       </c>
@@ -1738,7 +1746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45750</v>
       </c>
@@ -1749,7 +1757,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45750</v>
       </c>
@@ -1760,7 +1768,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45750</v>
       </c>
@@ -1771,7 +1779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45750</v>
       </c>
@@ -1782,7 +1790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45750</v>
       </c>
@@ -1793,7 +1801,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45750</v>
       </c>
@@ -1804,7 +1812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45757</v>
       </c>
@@ -1815,7 +1823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45757</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45757</v>
       </c>
@@ -1837,7 +1845,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45757</v>
       </c>
@@ -1848,7 +1856,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45757</v>
       </c>
@@ -1859,7 +1867,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45757</v>
       </c>
@@ -1870,7 +1878,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45757</v>
       </c>
@@ -1881,7 +1889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45757</v>
       </c>
@@ -1892,7 +1900,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45757</v>
       </c>
@@ -1903,7 +1911,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45757</v>
       </c>
@@ -1914,7 +1922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45757</v>
       </c>
@@ -1925,7 +1933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45757</v>
       </c>
@@ -1936,7 +1944,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45771</v>
       </c>
@@ -1947,7 +1955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45771</v>
       </c>
@@ -1958,7 +1966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45771</v>
       </c>
@@ -1969,7 +1977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45771</v>
       </c>
@@ -1980,7 +1988,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45771</v>
       </c>
@@ -1991,7 +1999,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45771</v>
       </c>
@@ -2002,7 +2010,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45771</v>
       </c>
@@ -2013,7 +2021,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45771</v>
       </c>
@@ -2024,7 +2032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45771</v>
       </c>
@@ -2035,7 +2043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45771</v>
       </c>
@@ -2046,7 +2054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45771</v>
       </c>
@@ -2057,7 +2065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45771</v>
       </c>
@@ -2068,7 +2076,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45785</v>
       </c>
@@ -2079,7 +2087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45785</v>
       </c>
@@ -2090,7 +2098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45785</v>
       </c>
@@ -2101,7 +2109,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45785</v>
       </c>
@@ -2112,7 +2120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45785</v>
       </c>
@@ -2123,7 +2131,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45785</v>
       </c>
@@ -2134,7 +2142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45785</v>
       </c>
@@ -2145,7 +2153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45785</v>
       </c>
@@ -2156,7 +2164,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45785</v>
       </c>
@@ -2167,7 +2175,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45785</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45785</v>
       </c>
@@ -2189,7 +2197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45785</v>
       </c>
@@ -2200,7 +2208,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45799</v>
       </c>
@@ -2211,7 +2219,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45799</v>
       </c>
@@ -2222,7 +2230,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45799</v>
       </c>
@@ -2233,7 +2241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45799</v>
       </c>
@@ -2244,7 +2252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45799</v>
       </c>
@@ -2255,7 +2263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45799</v>
       </c>
@@ -2266,7 +2274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45799</v>
       </c>
@@ -2277,7 +2285,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45799</v>
       </c>
@@ -2288,7 +2296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45799</v>
       </c>
@@ -2299,7 +2307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45799</v>
       </c>
@@ -2310,7 +2318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45799</v>
       </c>
@@ -2321,7 +2329,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45799</v>
       </c>
@@ -2332,7 +2340,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45806</v>
       </c>
@@ -2343,7 +2351,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45806</v>
       </c>
@@ -2354,7 +2362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45806</v>
       </c>
@@ -2365,7 +2373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45806</v>
       </c>
@@ -2376,7 +2384,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45806</v>
       </c>
@@ -2387,7 +2395,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45806</v>
       </c>
@@ -2398,7 +2406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45806</v>
       </c>
@@ -2409,7 +2417,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45806</v>
       </c>
@@ -2420,7 +2428,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45806</v>
       </c>
@@ -2431,7 +2439,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45806</v>
       </c>
@@ -2442,7 +2450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45806</v>
       </c>
@@ -2453,7 +2461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45806</v>
       </c>
@@ -2464,7 +2472,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45813</v>
       </c>
@@ -2475,7 +2483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45813</v>
       </c>
@@ -2486,7 +2494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45813</v>
       </c>
@@ -2497,7 +2505,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45813</v>
       </c>
@@ -2508,7 +2516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45813</v>
       </c>
@@ -2519,7 +2527,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45813</v>
       </c>
@@ -2530,7 +2538,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45813</v>
       </c>
@@ -2541,7 +2549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45813</v>
       </c>
@@ -2552,7 +2560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45813</v>
       </c>
@@ -2563,7 +2571,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45813</v>
       </c>
@@ -2574,7 +2582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45813</v>
       </c>
@@ -2585,7 +2593,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45813</v>
       </c>
@@ -2596,7 +2604,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45820</v>
       </c>
@@ -2607,7 +2615,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45820</v>
       </c>
@@ -2618,7 +2626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45820</v>
       </c>
@@ -2629,7 +2637,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45820</v>
       </c>
@@ -2640,7 +2648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45820</v>
       </c>
@@ -2651,7 +2659,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45820</v>
       </c>
@@ -2662,7 +2670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45820</v>
       </c>
@@ -2673,7 +2681,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45820</v>
       </c>
@@ -2684,7 +2692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45820</v>
       </c>
@@ -2695,7 +2703,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45820</v>
       </c>
@@ -2706,7 +2714,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45820</v>
       </c>
@@ -2717,7 +2725,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45820</v>
       </c>
@@ -2728,7 +2736,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45827</v>
       </c>
@@ -2739,7 +2747,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45827</v>
       </c>
@@ -2750,7 +2758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45827</v>
       </c>
@@ -2761,7 +2769,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45827</v>
       </c>
@@ -2772,7 +2780,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45827</v>
       </c>
@@ -2783,7 +2791,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45827</v>
       </c>
@@ -2794,7 +2802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45827</v>
       </c>
@@ -2805,7 +2813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45827</v>
       </c>
@@ -2816,7 +2824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45827</v>
       </c>
@@ -2827,7 +2835,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45827</v>
       </c>
@@ -2838,7 +2846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45827</v>
       </c>
@@ -2849,7 +2857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45827</v>
       </c>
@@ -2860,7 +2868,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45834</v>
       </c>
@@ -2871,7 +2879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45834</v>
       </c>
@@ -2882,7 +2890,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45834</v>
       </c>
@@ -2893,7 +2901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45834</v>
       </c>
@@ -2904,7 +2912,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45834</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45834</v>
       </c>
@@ -2926,7 +2934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45834</v>
       </c>
@@ -2937,7 +2945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45834</v>
       </c>
@@ -2948,7 +2956,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45834</v>
       </c>
@@ -2959,7 +2967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45834</v>
       </c>
@@ -2970,7 +2978,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45834</v>
       </c>
@@ -2981,7 +2989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45834</v>
       </c>
@@ -2993,20 +3001,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C73"/>
+  <autoFilter ref="A1:C73" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E363"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E413"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3020,7 +3028,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45722</v>
       </c>
@@ -3034,7 +3042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45722</v>
       </c>
@@ -3048,7 +3056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45722</v>
       </c>
@@ -3062,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45722</v>
       </c>
@@ -3076,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45722</v>
       </c>
@@ -3090,7 +3098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45722</v>
       </c>
@@ -3104,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45722</v>
       </c>
@@ -3118,7 +3126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45722</v>
       </c>
@@ -3132,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45722</v>
       </c>
@@ -3146,7 +3154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45722</v>
       </c>
@@ -3160,7 +3168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45722</v>
       </c>
@@ -3174,7 +3182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45722</v>
       </c>
@@ -3188,7 +3196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45729</v>
       </c>
@@ -3202,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45729</v>
       </c>
@@ -3216,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45729</v>
       </c>
@@ -3230,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45729</v>
       </c>
@@ -3244,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45729</v>
       </c>
@@ -3258,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45729</v>
       </c>
@@ -3272,7 +3280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45729</v>
       </c>
@@ -3286,7 +3294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45729</v>
       </c>
@@ -3300,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45729</v>
       </c>
@@ -3314,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45729</v>
       </c>
@@ -3328,7 +3336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45729</v>
       </c>
@@ -3342,7 +3350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45729</v>
       </c>
@@ -3356,7 +3364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45736</v>
       </c>
@@ -3370,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45736</v>
       </c>
@@ -3384,7 +3392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45736</v>
       </c>
@@ -3398,7 +3406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45736</v>
       </c>
@@ -3412,7 +3420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45736</v>
       </c>
@@ -3426,7 +3434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45736</v>
       </c>
@@ -3440,7 +3448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45736</v>
       </c>
@@ -3454,7 +3462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45736</v>
       </c>
@@ -3468,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45736</v>
       </c>
@@ -3478,11 +3486,11 @@
       <c r="C34" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45736</v>
       </c>
@@ -3496,7 +3504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45736</v>
       </c>
@@ -3510,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45736</v>
       </c>
@@ -3524,7 +3532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45736</v>
       </c>
@@ -3538,7 +3546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45743</v>
       </c>
@@ -3552,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45743</v>
       </c>
@@ -3566,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45743</v>
       </c>
@@ -3580,7 +3588,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45743</v>
       </c>
@@ -3594,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45743</v>
       </c>
@@ -3608,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45743</v>
       </c>
@@ -3622,7 +3630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45743</v>
       </c>
@@ -3636,7 +3644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45743</v>
       </c>
@@ -3650,7 +3658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45743</v>
       </c>
@@ -3664,7 +3672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45743</v>
       </c>
@@ -3678,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45743</v>
       </c>
@@ -3692,7 +3700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45743</v>
       </c>
@@ -3706,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45750</v>
       </c>
@@ -3720,7 +3728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45750</v>
       </c>
@@ -3734,7 +3742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45750</v>
       </c>
@@ -3748,7 +3756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45750</v>
       </c>
@@ -3762,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45750</v>
       </c>
@@ -3776,7 +3784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45750</v>
       </c>
@@ -3790,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45750</v>
       </c>
@@ -3804,7 +3812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45750</v>
       </c>
@@ -3818,7 +3826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45750</v>
       </c>
@@ -3832,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45750</v>
       </c>
@@ -3846,7 +3854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45750</v>
       </c>
@@ -3860,7 +3868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45750</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45757</v>
       </c>
@@ -3888,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45757</v>
       </c>
@@ -3902,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45757</v>
       </c>
@@ -3916,7 +3924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45757</v>
       </c>
@@ -3930,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45757</v>
       </c>
@@ -3944,7 +3952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45757</v>
       </c>
@@ -3958,7 +3966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45757</v>
       </c>
@@ -3972,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45757</v>
       </c>
@@ -3986,7 +3994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45757</v>
       </c>
@@ -4000,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45757</v>
       </c>
@@ -4014,7 +4022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45757</v>
       </c>
@@ -4028,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45757</v>
       </c>
@@ -4042,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45771</v>
       </c>
@@ -4056,7 +4064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45771</v>
       </c>
@@ -4070,7 +4078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45771</v>
       </c>
@@ -4084,7 +4092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45771</v>
       </c>
@@ -4098,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45771</v>
       </c>
@@ -4112,7 +4120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45771</v>
       </c>
@@ -4126,7 +4134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45771</v>
       </c>
@@ -4140,7 +4148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45771</v>
       </c>
@@ -4154,7 +4162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45771</v>
       </c>
@@ -4168,7 +4176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45771</v>
       </c>
@@ -4182,7 +4190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45771</v>
       </c>
@@ -4196,7 +4204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45771</v>
       </c>
@@ -4210,7 +4218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45785</v>
       </c>
@@ -4224,7 +4232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45785</v>
       </c>
@@ -4238,7 +4246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45785</v>
       </c>
@@ -4252,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45785</v>
       </c>
@@ -4266,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45785</v>
       </c>
@@ -4280,7 +4288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45785</v>
       </c>
@@ -4294,7 +4302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45785</v>
       </c>
@@ -4308,7 +4316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45785</v>
       </c>
@@ -4322,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45785</v>
       </c>
@@ -4336,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45785</v>
       </c>
@@ -4350,7 +4358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45785</v>
       </c>
@@ -4364,7 +4372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45785</v>
       </c>
@@ -4378,7 +4386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45799</v>
       </c>
@@ -4392,7 +4400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45799</v>
       </c>
@@ -4406,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45799</v>
       </c>
@@ -4420,7 +4428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45799</v>
       </c>
@@ -4434,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45799</v>
       </c>
@@ -4448,7 +4456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45799</v>
       </c>
@@ -4462,7 +4470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45799</v>
       </c>
@@ -4476,7 +4484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45799</v>
       </c>
@@ -4490,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45799</v>
       </c>
@@ -4504,7 +4512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45799</v>
       </c>
@@ -4518,7 +4526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45799</v>
       </c>
@@ -4532,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45799</v>
       </c>
@@ -4546,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45799</v>
       </c>
@@ -4560,7 +4568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45806</v>
       </c>
@@ -4574,7 +4582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45806</v>
       </c>
@@ -4588,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45806</v>
       </c>
@@ -4602,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45806</v>
       </c>
@@ -4616,7 +4624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45806</v>
       </c>
@@ -4630,7 +4638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45806</v>
       </c>
@@ -4644,7 +4652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45806</v>
       </c>
@@ -4658,7 +4666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45806</v>
       </c>
@@ -4672,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45806</v>
       </c>
@@ -4686,7 +4694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45806</v>
       </c>
@@ -4700,7 +4708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45806</v>
       </c>
@@ -4714,7 +4722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45806</v>
       </c>
@@ -4728,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45813</v>
       </c>
@@ -4742,7 +4750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45813</v>
       </c>
@@ -4756,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45813</v>
       </c>
@@ -4770,7 +4778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45813</v>
       </c>
@@ -4784,7 +4792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45813</v>
       </c>
@@ -4798,7 +4806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45813</v>
       </c>
@@ -4812,7 +4820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45813</v>
       </c>
@@ -4826,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45813</v>
       </c>
@@ -4840,7 +4848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45813</v>
       </c>
@@ -4854,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45813</v>
       </c>
@@ -4868,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45813</v>
       </c>
@@ -4882,7 +4890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45813</v>
       </c>
@@ -4896,7 +4904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45820</v>
       </c>
@@ -4910,7 +4918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45820</v>
       </c>
@@ -4924,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45820</v>
       </c>
@@ -4938,7 +4946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45820</v>
       </c>
@@ -4952,7 +4960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45820</v>
       </c>
@@ -4966,7 +4974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45820</v>
       </c>
@@ -4980,7 +4988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45820</v>
       </c>
@@ -4994,7 +5002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45820</v>
       </c>
@@ -5008,7 +5016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45820</v>
       </c>
@@ -5022,7 +5030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45820</v>
       </c>
@@ -5036,7 +5044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45820</v>
       </c>
@@ -5050,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45820</v>
       </c>
@@ -5064,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45827</v>
       </c>
@@ -5078,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45827</v>
       </c>
@@ -5092,7 +5100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45827</v>
       </c>
@@ -5106,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45827</v>
       </c>
@@ -5120,7 +5128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45827</v>
       </c>
@@ -5134,7 +5142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45827</v>
       </c>
@@ -5148,7 +5156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45827</v>
       </c>
@@ -5162,7 +5170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45827</v>
       </c>
@@ -5176,7 +5184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45827</v>
       </c>
@@ -5190,7 +5198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45827</v>
       </c>
@@ -5204,7 +5212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45827</v>
       </c>
@@ -5218,7 +5226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45827</v>
       </c>
@@ -5232,7 +5240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45834</v>
       </c>
@@ -5246,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45834</v>
       </c>
@@ -5260,7 +5268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45834</v>
       </c>
@@ -5274,7 +5282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45834</v>
       </c>
@@ -5288,7 +5296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45834</v>
       </c>
@@ -5302,7 +5310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45834</v>
       </c>
@@ -5316,7 +5324,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45834</v>
       </c>
@@ -5330,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45834</v>
       </c>
@@ -5344,7 +5352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45834</v>
       </c>
@@ -5358,7 +5366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45834</v>
       </c>
@@ -5372,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45834</v>
       </c>
@@ -5386,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45834</v>
       </c>
@@ -5400,7 +5408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45841</v>
       </c>
@@ -5414,7 +5422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>45841</v>
       </c>
@@ -5428,7 +5436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>45841</v>
       </c>
@@ -5442,7 +5450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>45841</v>
       </c>
@@ -5456,7 +5464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>45841</v>
       </c>
@@ -5466,11 +5474,11 @@
       <c r="C176" t="s">
         <v>2</v>
       </c>
-      <c r="D176" s="3">
+      <c r="D176" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>45841</v>
       </c>
@@ -5484,7 +5492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>45841</v>
       </c>
@@ -5498,7 +5506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>45841</v>
       </c>
@@ -5512,7 +5520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>45841</v>
       </c>
@@ -5526,7 +5534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>45841</v>
       </c>
@@ -5540,7 +5548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>45841</v>
       </c>
@@ -5554,7 +5562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>45841</v>
       </c>
@@ -5568,7 +5576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>45841</v>
       </c>
@@ -5582,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>45848</v>
       </c>
@@ -5596,7 +5604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>45848</v>
       </c>
@@ -5610,7 +5618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>45848</v>
       </c>
@@ -5624,7 +5632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>45848</v>
       </c>
@@ -5638,7 +5646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>45848</v>
       </c>
@@ -5652,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>45848</v>
       </c>
@@ -5666,7 +5674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>45848</v>
       </c>
@@ -5680,7 +5688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>45848</v>
       </c>
@@ -5694,7 +5702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>45848</v>
       </c>
@@ -5708,7 +5716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>45848</v>
       </c>
@@ -5722,7 +5730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>45848</v>
       </c>
@@ -5736,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>45848</v>
       </c>
@@ -5750,7 +5758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>45855</v>
       </c>
@@ -5764,7 +5772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>45855</v>
       </c>
@@ -5778,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>45855</v>
       </c>
@@ -5792,7 +5800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>45855</v>
       </c>
@@ -5806,7 +5814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>45855</v>
       </c>
@@ -5820,7 +5828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>45855</v>
       </c>
@@ -5834,7 +5842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>45855</v>
       </c>
@@ -5848,7 +5856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>45855</v>
       </c>
@@ -5862,7 +5870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>45855</v>
       </c>
@@ -5876,7 +5884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>45855</v>
       </c>
@@ -5890,7 +5898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>45855</v>
       </c>
@@ -5904,7 +5912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>45855</v>
       </c>
@@ -5918,7 +5926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>45862</v>
       </c>
@@ -5932,7 +5940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>45862</v>
       </c>
@@ -5946,7 +5954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>45862</v>
       </c>
@@ -5960,7 +5968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>45862</v>
       </c>
@@ -5974,7 +5982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>45862</v>
       </c>
@@ -5988,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>45862</v>
       </c>
@@ -6002,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>45862</v>
       </c>
@@ -6016,7 +6024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>45862</v>
       </c>
@@ -6030,7 +6038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>45862</v>
       </c>
@@ -6044,7 +6052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>45862</v>
       </c>
@@ -6058,7 +6066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>45862</v>
       </c>
@@ -6072,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>45862</v>
       </c>
@@ -6086,7 +6094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>45869</v>
       </c>
@@ -6100,7 +6108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>45869</v>
       </c>
@@ -6114,7 +6122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>45869</v>
       </c>
@@ -6128,7 +6136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>45869</v>
       </c>
@@ -6142,7 +6150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>45869</v>
       </c>
@@ -6156,7 +6164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>45869</v>
       </c>
@@ -6170,7 +6178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>45869</v>
       </c>
@@ -6184,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>45869</v>
       </c>
@@ -6198,7 +6206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>45869</v>
       </c>
@@ -6212,7 +6220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>45869</v>
       </c>
@@ -6226,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>45869</v>
       </c>
@@ -6240,7 +6248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>45869</v>
       </c>
@@ -6254,7 +6262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>45876</v>
       </c>
@@ -6268,7 +6276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>45876</v>
       </c>
@@ -6282,7 +6290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>45876</v>
       </c>
@@ -6296,7 +6304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>45876</v>
       </c>
@@ -6310,7 +6318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>45876</v>
       </c>
@@ -6324,7 +6332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>45876</v>
       </c>
@@ -6338,7 +6346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>45876</v>
       </c>
@@ -6352,7 +6360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>45876</v>
       </c>
@@ -6366,7 +6374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>45876</v>
       </c>
@@ -6380,7 +6388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>45876</v>
       </c>
@@ -6394,7 +6402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>45876</v>
       </c>
@@ -6408,7 +6416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>45876</v>
       </c>
@@ -6422,7 +6430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>45883</v>
       </c>
@@ -6436,7 +6444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>45883</v>
       </c>
@@ -6450,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>45883</v>
       </c>
@@ -6464,7 +6472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>45883</v>
       </c>
@@ -6478,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>45883</v>
       </c>
@@ -6492,7 +6500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>45883</v>
       </c>
@@ -6506,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>45883</v>
       </c>
@@ -6520,7 +6528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>45883</v>
       </c>
@@ -6534,7 +6542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>45883</v>
       </c>
@@ -6548,7 +6556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>45883</v>
       </c>
@@ -6562,7 +6570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>45904</v>
       </c>
@@ -6576,7 +6584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>45904</v>
       </c>
@@ -6590,7 +6598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>45904</v>
       </c>
@@ -6604,7 +6612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>45904</v>
       </c>
@@ -6618,7 +6626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>45904</v>
       </c>
@@ -6632,7 +6640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>45904</v>
       </c>
@@ -6646,7 +6654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>45904</v>
       </c>
@@ -6660,7 +6668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>45904</v>
       </c>
@@ -6674,7 +6682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>45904</v>
       </c>
@@ -6688,7 +6696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>45904</v>
       </c>
@@ -6702,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>45904</v>
       </c>
@@ -6716,7 +6724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>45904</v>
       </c>
@@ -6730,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>45918</v>
       </c>
@@ -6744,7 +6752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>45918</v>
       </c>
@@ -6758,7 +6766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>45918</v>
       </c>
@@ -6772,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>45918</v>
       </c>
@@ -6786,7 +6794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>45918</v>
       </c>
@@ -6800,7 +6808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>45918</v>
       </c>
@@ -6814,7 +6822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45918</v>
       </c>
@@ -6828,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45918</v>
       </c>
@@ -6842,7 +6850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45918</v>
       </c>
@@ -6856,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45918</v>
       </c>
@@ -6870,7 +6878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45918</v>
       </c>
@@ -6884,7 +6892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>45918</v>
       </c>
@@ -6898,7 +6906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>45925</v>
       </c>
@@ -6912,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>45925</v>
       </c>
@@ -6926,7 +6934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>45925</v>
       </c>
@@ -6940,7 +6948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45925</v>
       </c>
@@ -6954,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>45925</v>
       </c>
@@ -6968,7 +6976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>45925</v>
       </c>
@@ -6982,7 +6990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>45925</v>
       </c>
@@ -6996,7 +7004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>45925</v>
       </c>
@@ -7010,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>45925</v>
       </c>
@@ -7024,7 +7032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>45925</v>
       </c>
@@ -7038,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>45925</v>
       </c>
@@ -7052,7 +7060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>45925</v>
       </c>
@@ -7066,7 +7074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>45932</v>
       </c>
@@ -7080,7 +7088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>45932</v>
       </c>
@@ -7094,7 +7102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>45932</v>
       </c>
@@ -7108,7 +7116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>45932</v>
       </c>
@@ -7122,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>45932</v>
       </c>
@@ -7136,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>45932</v>
       </c>
@@ -7150,7 +7158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>45932</v>
       </c>
@@ -7164,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>45932</v>
       </c>
@@ -7178,7 +7186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>45932</v>
       </c>
@@ -7192,7 +7200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>45932</v>
       </c>
@@ -7206,7 +7214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>45932</v>
       </c>
@@ -7220,7 +7228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>45932</v>
       </c>
@@ -7234,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>45939</v>
       </c>
@@ -7248,7 +7256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>45939</v>
       </c>
@@ -7262,7 +7270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>45939</v>
       </c>
@@ -7276,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>45939</v>
       </c>
@@ -7290,7 +7298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>45939</v>
       </c>
@@ -7304,7 +7312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>45939</v>
       </c>
@@ -7318,7 +7326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>45939</v>
       </c>
@@ -7332,7 +7340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>45939</v>
       </c>
@@ -7346,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>45939</v>
       </c>
@@ -7360,7 +7368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>45939</v>
       </c>
@@ -7374,7 +7382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>45939</v>
       </c>
@@ -7388,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>45939</v>
       </c>
@@ -7402,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>45946</v>
       </c>
@@ -7416,7 +7424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>45946</v>
       </c>
@@ -7430,7 +7438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>45946</v>
       </c>
@@ -7444,7 +7452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>45946</v>
       </c>
@@ -7458,7 +7466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>45946</v>
       </c>
@@ -7472,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>45946</v>
       </c>
@@ -7486,7 +7494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>45946</v>
       </c>
@@ -7500,7 +7508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>45946</v>
       </c>
@@ -7514,7 +7522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>45946</v>
       </c>
@@ -7528,7 +7536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>45946</v>
       </c>
@@ -7542,7 +7550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>45946</v>
       </c>
@@ -7556,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>45946</v>
       </c>
@@ -7570,7 +7578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>45946</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>45960</v>
       </c>
@@ -7598,7 +7606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>45960</v>
       </c>
@@ -7612,7 +7620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>45960</v>
       </c>
@@ -7626,7 +7634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>45960</v>
       </c>
@@ -7640,7 +7648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>45960</v>
       </c>
@@ -7654,7 +7662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>45960</v>
       </c>
@@ -7668,7 +7676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>45960</v>
       </c>
@@ -7682,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>45960</v>
       </c>
@@ -7696,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>45960</v>
       </c>
@@ -7710,7 +7718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>45960</v>
       </c>
@@ -7724,7 +7732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>45960</v>
       </c>
@@ -7738,7 +7746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>45960</v>
       </c>
@@ -7752,7 +7760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>45967</v>
       </c>
@@ -7766,7 +7774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>45967</v>
       </c>
@@ -7780,7 +7788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>45967</v>
       </c>
@@ -7794,7 +7802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>45967</v>
       </c>
@@ -7808,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>45967</v>
       </c>
@@ -7822,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>45967</v>
       </c>
@@ -7840,7 +7848,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>45967</v>
       </c>
@@ -7854,7 +7862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>45967</v>
       </c>
@@ -7868,7 +7876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>45967</v>
       </c>
@@ -7882,7 +7890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>45967</v>
       </c>
@@ -7896,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>45967</v>
       </c>
@@ -7910,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>45967</v>
       </c>
@@ -7928,7 +7936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>45974</v>
       </c>
@@ -7938,11 +7946,11 @@
       <c r="C352" t="s">
         <v>2</v>
       </c>
-      <c r="D352" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D352" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>45974</v>
       </c>
@@ -7952,11 +7960,11 @@
       <c r="C353" t="s">
         <v>48</v>
       </c>
-      <c r="D353" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>45974</v>
       </c>
@@ -7970,7 +7978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>45974</v>
       </c>
@@ -7984,7 +7992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>45974</v>
       </c>
@@ -7998,7 +8006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>45974</v>
       </c>
@@ -8008,7 +8016,7 @@
       <c r="C357" t="s">
         <v>76</v>
       </c>
-      <c r="D357" s="4">
+      <c r="D357" s="3">
         <v>1</v>
       </c>
       <c r="E357">
@@ -8016,7 +8024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>45974</v>
       </c>
@@ -8030,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>45974</v>
       </c>
@@ -8044,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>45974</v>
       </c>
@@ -8058,7 +8066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>45974</v>
       </c>
@@ -8072,7 +8080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>45974</v>
       </c>
@@ -8086,7 +8094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>45974</v>
       </c>
@@ -8104,18 +8112,750 @@
         <v>6</v>
       </c>
     </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A364" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1</v>
+      </c>
+      <c r="C364" t="s">
+        <v>16</v>
+      </c>
+      <c r="D364">
+        <v>3</v>
+      </c>
+      <c r="E364">
+        <f>SUM(D364:D368)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A365" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1</v>
+      </c>
+      <c r="C365" t="s">
+        <v>20</v>
+      </c>
+      <c r="D365">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A366" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1</v>
+      </c>
+      <c r="C366" t="s">
+        <v>14</v>
+      </c>
+      <c r="D366">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1</v>
+      </c>
+      <c r="C367" t="s">
+        <v>45</v>
+      </c>
+      <c r="D367">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1</v>
+      </c>
+      <c r="C368" t="s">
+        <v>28</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B369" t="s">
+        <v>17</v>
+      </c>
+      <c r="C369" t="s">
+        <v>48</v>
+      </c>
+      <c r="D369">
+        <v>2</v>
+      </c>
+      <c r="E369">
+        <f>SUM(D369:D373)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B370" t="s">
+        <v>17</v>
+      </c>
+      <c r="C370" t="s">
+        <v>30</v>
+      </c>
+      <c r="D370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B371" t="s">
+        <v>17</v>
+      </c>
+      <c r="C371" t="s">
+        <v>71</v>
+      </c>
+      <c r="D371">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A372" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B372" t="s">
+        <v>17</v>
+      </c>
+      <c r="C372" t="s">
+        <v>9</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B373" t="s">
+        <v>17</v>
+      </c>
+      <c r="C373" t="s">
+        <v>10</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B374" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" t="s">
+        <v>2</v>
+      </c>
+      <c r="D374">
+        <v>4</v>
+      </c>
+      <c r="E374">
+        <f>SUM(D374:D378)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A375" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B375" t="s">
+        <v>17</v>
+      </c>
+      <c r="C375" t="s">
+        <v>85</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A376" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B376" t="s">
+        <v>17</v>
+      </c>
+      <c r="C376" t="s">
+        <v>51</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B377" t="s">
+        <v>17</v>
+      </c>
+      <c r="C377" t="s">
+        <v>28</v>
+      </c>
+      <c r="D377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A378" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B378" t="s">
+        <v>17</v>
+      </c>
+      <c r="C378" t="s">
+        <v>41</v>
+      </c>
+      <c r="D378">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1</v>
+      </c>
+      <c r="C379" t="s">
+        <v>14</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <f>SUM(D379:D383)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1</v>
+      </c>
+      <c r="C380" t="s">
+        <v>30</v>
+      </c>
+      <c r="D380">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1</v>
+      </c>
+      <c r="C381" t="s">
+        <v>20</v>
+      </c>
+      <c r="D381">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1</v>
+      </c>
+      <c r="C382" t="s">
+        <v>10</v>
+      </c>
+      <c r="D382">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1</v>
+      </c>
+      <c r="C383" t="s">
+        <v>48</v>
+      </c>
+      <c r="D383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1</v>
+      </c>
+      <c r="C384" t="s">
+        <v>47</v>
+      </c>
+      <c r="D384">
+        <v>1</v>
+      </c>
+      <c r="E384">
+        <f>SUM(D384:D388)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1</v>
+      </c>
+      <c r="C385" t="s">
+        <v>22</v>
+      </c>
+      <c r="D385">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1</v>
+      </c>
+      <c r="C386" t="s">
+        <v>14</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1</v>
+      </c>
+      <c r="C387" t="s">
+        <v>51</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1</v>
+      </c>
+      <c r="C388" t="s">
+        <v>41</v>
+      </c>
+      <c r="D388">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B389" t="s">
+        <v>17</v>
+      </c>
+      <c r="C389" t="s">
+        <v>16</v>
+      </c>
+      <c r="D389">
+        <v>2</v>
+      </c>
+      <c r="E389">
+        <f>SUM(D389:D393)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B390" t="s">
+        <v>17</v>
+      </c>
+      <c r="C390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B391" t="s">
+        <v>17</v>
+      </c>
+      <c r="C391" t="s">
+        <v>10</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B392" t="s">
+        <v>17</v>
+      </c>
+      <c r="C392" t="s">
+        <v>20</v>
+      </c>
+      <c r="D392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B393" t="s">
+        <v>17</v>
+      </c>
+      <c r="C393" t="s">
+        <v>76</v>
+      </c>
+      <c r="D393">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1</v>
+      </c>
+      <c r="C394" t="s">
+        <v>20</v>
+      </c>
+      <c r="D394">
+        <v>3</v>
+      </c>
+      <c r="E394">
+        <f>SUM(D394:D398)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1</v>
+      </c>
+      <c r="C395" t="s">
+        <v>48</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1</v>
+      </c>
+      <c r="C396" t="s">
+        <v>33</v>
+      </c>
+      <c r="D396">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1</v>
+      </c>
+      <c r="C397" t="s">
+        <v>9</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1</v>
+      </c>
+      <c r="C398" t="s">
+        <v>76</v>
+      </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B399" t="s">
+        <v>17</v>
+      </c>
+      <c r="C399" t="s">
+        <v>2</v>
+      </c>
+      <c r="D399">
+        <v>2</v>
+      </c>
+      <c r="E399">
+        <f>SUM(D399:D403)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B400" t="s">
+        <v>17</v>
+      </c>
+      <c r="C400" t="s">
+        <v>47</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B401" t="s">
+        <v>17</v>
+      </c>
+      <c r="C401" t="s">
+        <v>51</v>
+      </c>
+      <c r="D401">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B402" t="s">
+        <v>17</v>
+      </c>
+      <c r="C402" t="s">
+        <v>45</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B403" t="s">
+        <v>17</v>
+      </c>
+      <c r="C403" t="s">
+        <v>28</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1</v>
+      </c>
+      <c r="C404" t="s">
+        <v>16</v>
+      </c>
+      <c r="D404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1</v>
+      </c>
+      <c r="C405" t="s">
+        <v>14</v>
+      </c>
+      <c r="D405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1</v>
+      </c>
+      <c r="C406" t="s">
+        <v>33</v>
+      </c>
+      <c r="D406">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1</v>
+      </c>
+      <c r="C407" t="s">
+        <v>48</v>
+      </c>
+      <c r="D407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1</v>
+      </c>
+      <c r="C408" t="s">
+        <v>28</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B409" t="s">
+        <v>17</v>
+      </c>
+      <c r="C409" t="s">
+        <v>2</v>
+      </c>
+      <c r="D409">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B410" t="s">
+        <v>17</v>
+      </c>
+      <c r="C410" t="s">
+        <v>51</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B411" t="s">
+        <v>17</v>
+      </c>
+      <c r="C411" t="s">
+        <v>9</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B412" t="s">
+        <v>17</v>
+      </c>
+      <c r="C412" t="s">
+        <v>45</v>
+      </c>
+      <c r="D412">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B413" t="s">
+        <v>17</v>
+      </c>
+      <c r="C413" t="s">
+        <v>86</v>
+      </c>
+      <c r="D413">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D290"/>
+  <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>45960</v>
       </c>
@@ -8126,7 +8866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45960</v>
       </c>
@@ -8137,7 +8877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45967</v>
       </c>
@@ -8148,7 +8888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45967</v>
       </c>
@@ -8159,7 +8899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45974</v>
       </c>
@@ -8170,7 +8910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45974</v>
       </c>
@@ -8178,6 +8918,28 @@
         <v>84</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8187,11 +8949,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8202,7 +8964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45722</v>
       </c>
@@ -8213,7 +8975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45722</v>
       </c>
@@ -8224,7 +8986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45729</v>
       </c>
@@ -8235,7 +8997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45729</v>
       </c>
@@ -8246,7 +9008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45736</v>
       </c>
@@ -8257,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45736</v>
       </c>
@@ -8268,7 +9030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45743</v>
       </c>
@@ -8279,7 +9041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45743</v>
       </c>
@@ -8290,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45750</v>
       </c>
@@ -8301,7 +9063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45750</v>
       </c>
@@ -8312,7 +9074,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45757</v>
       </c>
@@ -8323,7 +9085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45757</v>
       </c>
@@ -8334,7 +9096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45771</v>
       </c>
@@ -8345,7 +9107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45771</v>
       </c>
@@ -8356,7 +9118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45785</v>
       </c>
@@ -8367,7 +9129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45785</v>
       </c>
@@ -8378,7 +9140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45799</v>
       </c>
@@ -8389,7 +9151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45799</v>
       </c>
@@ -8400,7 +9162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45806</v>
       </c>
@@ -8411,7 +9173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45806</v>
       </c>
@@ -8422,7 +9184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45813</v>
       </c>
@@ -8433,7 +9195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45813</v>
       </c>
@@ -8444,7 +9206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45820</v>
       </c>
@@ -8455,7 +9217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45820</v>
       </c>
@@ -8466,7 +9228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45827</v>
       </c>
@@ -8477,7 +9239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45827</v>
       </c>
@@ -8488,7 +9250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45834</v>
       </c>
@@ -8499,7 +9261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45834</v>
       </c>
@@ -8510,7 +9272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45841</v>
       </c>
@@ -8521,7 +9283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45841</v>
       </c>
@@ -8532,7 +9294,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45848</v>
       </c>
@@ -8543,7 +9305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45848</v>
       </c>
@@ -8554,7 +9316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45855</v>
       </c>
@@ -8565,7 +9327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45855</v>
       </c>
@@ -8576,7 +9338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45862</v>
       </c>
@@ -8587,7 +9349,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45862</v>
       </c>
@@ -8598,7 +9360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45869</v>
       </c>
@@ -8609,7 +9371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45869</v>
       </c>
@@ -8620,7 +9382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45876</v>
       </c>
@@ -8631,7 +9393,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45876</v>
       </c>
@@ -8642,7 +9404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45883</v>
       </c>
@@ -8653,7 +9415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45883</v>
       </c>
@@ -8664,7 +9426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45904</v>
       </c>
@@ -8675,7 +9437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45904</v>
       </c>
@@ -8686,7 +9448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45918</v>
       </c>
@@ -8697,7 +9459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45918</v>
       </c>
@@ -8708,7 +9470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45925</v>
       </c>
@@ -8719,7 +9481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45925</v>
       </c>
@@ -8730,7 +9492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45939</v>
       </c>
@@ -8741,7 +9503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45939</v>
       </c>
@@ -8752,7 +9514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45946</v>
       </c>
@@ -8763,7 +9525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45946</v>
       </c>
@@ -8774,7 +9536,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45960</v>
       </c>
@@ -8785,7 +9547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45960</v>
       </c>
@@ -8796,7 +9558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45967</v>
       </c>
@@ -8807,7 +9569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45967</v>
       </c>
@@ -8818,7 +9580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45974</v>
       </c>
@@ -8829,7 +9591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45974</v>
       </c>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F66EBB44-384C-4D0A-B157-D805CD792392}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD3AEE6-2608-49E9-8B8F-8CA3D16E17F8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="88">
   <si>
     <t>Fecha</t>
   </si>
@@ -307,6 +307,9 @@
   <si>
     <t>Chicho</t>
   </si>
+  <si>
+    <t>Hernan (amigo Pata)</t>
+  </si>
 </sst>
 </file>
 
@@ -373,6 +376,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -932,6 +939,11 @@
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E413"/>
+  <dimension ref="A1:E423"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -8662,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>46058</v>
       </c>
@@ -8676,7 +8688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>46058</v>
       </c>
@@ -8690,7 +8702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>46058</v>
       </c>
@@ -8704,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>46065</v>
       </c>
@@ -8718,7 +8730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>46065</v>
       </c>
@@ -8732,7 +8744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>46065</v>
       </c>
@@ -8746,7 +8758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>46065</v>
       </c>
@@ -8760,7 +8772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>46065</v>
       </c>
@@ -8774,7 +8786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>46065</v>
       </c>
@@ -8788,7 +8800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>46065</v>
       </c>
@@ -8802,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>46065</v>
       </c>
@@ -8816,7 +8828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>46065</v>
       </c>
@@ -8830,7 +8842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>46065</v>
       </c>
@@ -8842,6 +8854,154 @@
       </c>
       <c r="D413">
         <v>3</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1</v>
+      </c>
+      <c r="C414" t="s">
+        <v>2</v>
+      </c>
+      <c r="D414">
+        <v>4</v>
+      </c>
+      <c r="E414">
+        <f>SUM(D414:D418)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1</v>
+      </c>
+      <c r="C415" t="s">
+        <v>9</v>
+      </c>
+      <c r="D415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A416" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1</v>
+      </c>
+      <c r="C416" t="s">
+        <v>10</v>
+      </c>
+      <c r="D416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1</v>
+      </c>
+      <c r="C417" t="s">
+        <v>28</v>
+      </c>
+      <c r="D417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A418" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1</v>
+      </c>
+      <c r="C418" t="s">
+        <v>51</v>
+      </c>
+      <c r="D418">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A419" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B419" t="s">
+        <v>17</v>
+      </c>
+      <c r="C419" t="s">
+        <v>30</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+      <c r="E419">
+        <f>SUM(D419:D423)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A420" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B420" t="s">
+        <v>17</v>
+      </c>
+      <c r="C420" t="s">
+        <v>48</v>
+      </c>
+      <c r="D420">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A421" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B421" t="s">
+        <v>17</v>
+      </c>
+      <c r="C421" t="s">
+        <v>45</v>
+      </c>
+      <c r="D421">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A422" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B422" t="s">
+        <v>17</v>
+      </c>
+      <c r="C422" t="s">
+        <v>20</v>
+      </c>
+      <c r="D422">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A423" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B423" t="s">
+        <v>17</v>
+      </c>
+      <c r="C423" t="s">
+        <v>87</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD3AEE6-2608-49E9-8B8F-8CA3D16E17F8}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97697216-7AD1-4B85-B23E-8BFFD4EE1C9A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="89">
   <si>
     <t>Fecha</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>Hernan (amigo Pata)</t>
+  </si>
+  <si>
+    <t>Fiori</t>
   </si>
 </sst>
 </file>
@@ -953,7 +956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1013,57 +1016,57 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1071,72 +1074,64 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3020,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E423"/>
+  <dimension ref="A1:E433"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9002,6 +8997,154 @@
       </c>
       <c r="D423">
         <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1</v>
+      </c>
+      <c r="C424" t="s">
+        <v>14</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+      <c r="E424">
+        <f>SUM(D424:D428)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1</v>
+      </c>
+      <c r="C425" t="s">
+        <v>20</v>
+      </c>
+      <c r="D425">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A426" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1</v>
+      </c>
+      <c r="C426" t="s">
+        <v>30</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A427" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1</v>
+      </c>
+      <c r="C427" t="s">
+        <v>10</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A428" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1</v>
+      </c>
+      <c r="C428" t="s">
+        <v>45</v>
+      </c>
+      <c r="D428">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A429" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B429" t="s">
+        <v>17</v>
+      </c>
+      <c r="C429" t="s">
+        <v>16</v>
+      </c>
+      <c r="D429">
+        <v>1</v>
+      </c>
+      <c r="E429">
+        <f>SUM(D429:D433)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B430" t="s">
+        <v>17</v>
+      </c>
+      <c r="C430" t="s">
+        <v>48</v>
+      </c>
+      <c r="D430">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A431" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B431" t="s">
+        <v>17</v>
+      </c>
+      <c r="C431" t="s">
+        <v>9</v>
+      </c>
+      <c r="D431">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A432" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B432" t="s">
+        <v>17</v>
+      </c>
+      <c r="C432" t="s">
+        <v>51</v>
+      </c>
+      <c r="D432">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A433" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B433" t="s">
+        <v>17</v>
+      </c>
+      <c r="C433" t="s">
+        <v>28</v>
+      </c>
+      <c r="D433">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97697216-7AD1-4B85-B23E-8BFFD4EE1C9A}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CDC840-7287-4788-8DA8-43DAB689B519}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="89">
   <si>
     <t>Fecha</t>
   </si>
@@ -3015,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E433"/>
+  <dimension ref="A1:E446"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9133,7 +9133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>46079</v>
       </c>
@@ -9146,6 +9146,163 @@
       <c r="D433">
         <v>2</v>
       </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A434" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1</v>
+      </c>
+      <c r="C434" t="s">
+        <v>2</v>
+      </c>
+      <c r="D434">
+        <v>3</v>
+      </c>
+      <c r="E434">
+        <f>SUM(D434:D438)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A435" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1</v>
+      </c>
+      <c r="C435" t="s">
+        <v>48</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A436" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1</v>
+      </c>
+      <c r="C436" t="s">
+        <v>14</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A437" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1</v>
+      </c>
+      <c r="C437" t="s">
+        <v>20</v>
+      </c>
+      <c r="D437">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A438" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1</v>
+      </c>
+      <c r="C438" t="s">
+        <v>28</v>
+      </c>
+      <c r="D438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A439" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B439" t="s">
+        <v>17</v>
+      </c>
+      <c r="C439" t="s">
+        <v>69</v>
+      </c>
+      <c r="D439">
+        <v>1</v>
+      </c>
+      <c r="E439">
+        <f>SUM(D439:D443)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A440" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B440" t="s">
+        <v>17</v>
+      </c>
+      <c r="C440" t="s">
+        <v>10</v>
+      </c>
+      <c r="D440">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A441" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B441" t="s">
+        <v>17</v>
+      </c>
+      <c r="C441" t="s">
+        <v>9</v>
+      </c>
+      <c r="D441">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A442" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B442" t="s">
+        <v>17</v>
+      </c>
+      <c r="C442" t="s">
+        <v>51</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A443" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B443" t="s">
+        <v>17</v>
+      </c>
+      <c r="C443" t="s">
+        <v>71</v>
+      </c>
+      <c r="D443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A444" s="1"/>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A445" s="1"/>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A446" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CDC840-7287-4788-8DA8-43DAB689B519}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF126FBC-42DD-4F18-AF2B-F8C14C8DD569}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>Fiori</t>
+  </si>
+  <si>
+    <t>Tomi</t>
   </si>
 </sst>
 </file>
@@ -648,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -947,6 +950,11 @@
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E446"/>
+  <dimension ref="A1:E455"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9296,13 +9304,169 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A444" s="1"/>
+      <c r="A444" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1</v>
+      </c>
+      <c r="C444" t="s">
+        <v>20</v>
+      </c>
+      <c r="D444">
+        <v>2</v>
+      </c>
+      <c r="E444">
+        <f>SUM(D444:D448)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A445" s="1"/>
+      <c r="A445" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1</v>
+      </c>
+      <c r="C445" t="s">
+        <v>10</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A446" s="1"/>
+      <c r="A446" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1</v>
+      </c>
+      <c r="C446" t="s">
+        <v>47</v>
+      </c>
+      <c r="D446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A447" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1</v>
+      </c>
+      <c r="C447" t="s">
+        <v>89</v>
+      </c>
+      <c r="D447">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A448" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1</v>
+      </c>
+      <c r="C448" t="s">
+        <v>30</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A449" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B449" t="s">
+        <v>17</v>
+      </c>
+      <c r="C449" t="s">
+        <v>51</v>
+      </c>
+      <c r="D449">
+        <v>1</v>
+      </c>
+      <c r="E449">
+        <f>SUM(D449:D454)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A450" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B450" t="s">
+        <v>17</v>
+      </c>
+      <c r="C450" t="s">
+        <v>9</v>
+      </c>
+      <c r="D450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A451" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B451" t="s">
+        <v>17</v>
+      </c>
+      <c r="C451" t="s">
+        <v>48</v>
+      </c>
+      <c r="D451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A452" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B452" t="s">
+        <v>17</v>
+      </c>
+      <c r="C452" t="s">
+        <v>45</v>
+      </c>
+      <c r="D452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A453" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B453" t="s">
+        <v>17</v>
+      </c>
+      <c r="C453" t="s">
+        <v>16</v>
+      </c>
+      <c r="D453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A454" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B454" t="s">
+        <v>17</v>
+      </c>
+      <c r="C454" t="s">
+        <v>54</v>
+      </c>
+      <c r="D454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A455" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF126FBC-42DD-4F18-AF2B-F8C14C8DD569}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1605F1-15B3-4DE6-A789-85ECA8C7E115}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -3023,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E455"/>
+  <dimension ref="A1:E465"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9466,7 +9466,155 @@
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A455" s="1"/>
+      <c r="A455" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1</v>
+      </c>
+      <c r="C455" t="s">
+        <v>16</v>
+      </c>
+      <c r="D455">
+        <v>1</v>
+      </c>
+      <c r="E455">
+        <f>SUM(D455:D459)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A456" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1</v>
+      </c>
+      <c r="C456" t="s">
+        <v>48</v>
+      </c>
+      <c r="D456">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A457" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1</v>
+      </c>
+      <c r="C457" t="s">
+        <v>51</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A458" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1</v>
+      </c>
+      <c r="C458" t="s">
+        <v>20</v>
+      </c>
+      <c r="D458">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A459" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1</v>
+      </c>
+      <c r="C459" t="s">
+        <v>28</v>
+      </c>
+      <c r="D459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A460" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B460" t="s">
+        <v>17</v>
+      </c>
+      <c r="C460" t="s">
+        <v>30</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460">
+        <f>SUM(D460:D464)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A461" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B461" t="s">
+        <v>17</v>
+      </c>
+      <c r="C461" t="s">
+        <v>69</v>
+      </c>
+      <c r="D461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A462" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B462" t="s">
+        <v>17</v>
+      </c>
+      <c r="C462" t="s">
+        <v>9</v>
+      </c>
+      <c r="D462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A463" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B463" t="s">
+        <v>17</v>
+      </c>
+      <c r="C463" t="s">
+        <v>10</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A464" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B464" t="s">
+        <v>17</v>
+      </c>
+      <c r="C464" t="s">
+        <v>45</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A465" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1605F1-15B3-4DE6-A789-85ECA8C7E115}"/>
+  <xr:revisionPtr revIDLastSave="366" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EA5B438-5243-41EE-BC88-D9FB81F2D32D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -3023,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E465"/>
+  <dimension ref="A1:E474"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9613,8 +9613,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A465" s="1"/>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A465" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1</v>
+      </c>
+      <c r="C465" t="s">
+        <v>14</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465">
+        <f>SUM(D465:D469)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A466" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1</v>
+      </c>
+      <c r="C466" t="s">
+        <v>20</v>
+      </c>
+      <c r="D466">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A467" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1</v>
+      </c>
+      <c r="C467" t="s">
+        <v>16</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A468" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1</v>
+      </c>
+      <c r="C468" t="s">
+        <v>45</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A469" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1</v>
+      </c>
+      <c r="C469" t="s">
+        <v>10</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A470" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B470" t="s">
+        <v>17</v>
+      </c>
+      <c r="C470" t="s">
+        <v>28</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <f>SUM(D470:D474)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A471" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B471" t="s">
+        <v>17</v>
+      </c>
+      <c r="C471" t="s">
+        <v>9</v>
+      </c>
+      <c r="D471">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A472" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B472" t="s">
+        <v>17</v>
+      </c>
+      <c r="C472" t="s">
+        <v>51</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A473" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B473" t="s">
+        <v>17</v>
+      </c>
+      <c r="C473" t="s">
+        <v>30</v>
+      </c>
+      <c r="D473">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A474" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B474" t="s">
+        <v>17</v>
+      </c>
+      <c r="C474" t="s">
+        <v>2</v>
+      </c>
+      <c r="D474">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="366" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EA5B438-5243-41EE-BC88-D9FB81F2D32D}"/>
+  <xr:revisionPtr revIDLastSave="369" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F5ABF0-B33A-4337-883E-1B6FE5473015}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="E465">
         <f>SUM(D465:D469)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
@@ -9670,7 +9670,7 @@
         <v>45</v>
       </c>
       <c r="D468">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="E470">
         <f>SUM(D470:D474)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
@@ -9758,7 +9758,7 @@
         <v>2</v>
       </c>
       <c r="D474">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="369" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F5ABF0-B33A-4337-883E-1B6FE5473015}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0784CD45-64D7-40FE-B025-5E4AFB0A00D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -384,10 +384,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -3023,7 +3019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E474"/>
+  <dimension ref="A1:E485"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9759,6 +9755,168 @@
       </c>
       <c r="D474">
         <v>4</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1</v>
+      </c>
+      <c r="C475" t="s">
+        <v>14</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <f>SUM(D475:D479)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A476" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1</v>
+      </c>
+      <c r="C476" t="s">
+        <v>47</v>
+      </c>
+      <c r="D476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A477" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1</v>
+      </c>
+      <c r="C477" t="s">
+        <v>20</v>
+      </c>
+      <c r="D477">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A478" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1</v>
+      </c>
+      <c r="C478" t="s">
+        <v>43</v>
+      </c>
+      <c r="D478">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A479" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1</v>
+      </c>
+      <c r="C479" t="s">
+        <v>71</v>
+      </c>
+      <c r="D479">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A480" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B480" t="s">
+        <v>17</v>
+      </c>
+      <c r="C480" t="s">
+        <v>9</v>
+      </c>
+      <c r="D480">
+        <v>1</v>
+      </c>
+      <c r="E480">
+        <f>SUM(D480:D485)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A481" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B481" t="s">
+        <v>17</v>
+      </c>
+      <c r="C481" t="s">
+        <v>48</v>
+      </c>
+      <c r="D481">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A482" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B482" t="s">
+        <v>17</v>
+      </c>
+      <c r="C482" t="s">
+        <v>51</v>
+      </c>
+      <c r="D482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A483" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B483" t="s">
+        <v>17</v>
+      </c>
+      <c r="C483" t="s">
+        <v>2</v>
+      </c>
+      <c r="D483">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A484" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B484" t="s">
+        <v>17</v>
+      </c>
+      <c r="C484" t="s">
+        <v>65</v>
+      </c>
+      <c r="D484">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A485" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B485" t="s">
+        <v>17</v>
+      </c>
+      <c r="C485" t="s">
+        <v>54</v>
+      </c>
+      <c r="D485">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0784CD45-64D7-40FE-B025-5E4AFB0A00D7}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF0DA90D-CDAD-4226-90EF-7980EBED3947}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -384,6 +384,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -3019,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E485"/>
+  <dimension ref="A1:E495"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -9849,7 +9853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>46121</v>
       </c>
@@ -9863,7 +9867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>46121</v>
       </c>
@@ -9877,7 +9881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>46121</v>
       </c>
@@ -9891,7 +9895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>46121</v>
       </c>
@@ -9905,7 +9909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>46121</v>
       </c>
@@ -9917,6 +9921,154 @@
       </c>
       <c r="D485">
         <v>2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A486" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1</v>
+      </c>
+      <c r="C486" t="s">
+        <v>14</v>
+      </c>
+      <c r="D486">
+        <v>0</v>
+      </c>
+      <c r="E486">
+        <f>SUM(D486:D490)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A487" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1</v>
+      </c>
+      <c r="C487" t="s">
+        <v>47</v>
+      </c>
+      <c r="D487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1</v>
+      </c>
+      <c r="C488" t="s">
+        <v>20</v>
+      </c>
+      <c r="D488">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A489" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1</v>
+      </c>
+      <c r="C489" t="s">
+        <v>45</v>
+      </c>
+      <c r="D489">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A490" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1</v>
+      </c>
+      <c r="C490" t="s">
+        <v>69</v>
+      </c>
+      <c r="D490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A491" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B491" t="s">
+        <v>17</v>
+      </c>
+      <c r="C491" t="s">
+        <v>9</v>
+      </c>
+      <c r="D491">
+        <v>2</v>
+      </c>
+      <c r="E491">
+        <f>SUM(D491:D495)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A492" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B492" t="s">
+        <v>17</v>
+      </c>
+      <c r="C492" t="s">
+        <v>48</v>
+      </c>
+      <c r="D492">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A493" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B493" t="s">
+        <v>17</v>
+      </c>
+      <c r="C493" t="s">
+        <v>16</v>
+      </c>
+      <c r="D493">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A494" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B494" t="s">
+        <v>17</v>
+      </c>
+      <c r="C494" t="s">
+        <v>10</v>
+      </c>
+      <c r="D494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A495" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B495" t="s">
+        <v>17</v>
+      </c>
+      <c r="C495" t="s">
+        <v>65</v>
+      </c>
+      <c r="D495">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="422" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF0DA90D-CDAD-4226-90EF-7980EBED3947}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F44C760E-2D14-452A-A309-9345A29AA07B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -3023,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E495"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -10070,6 +10070,166 @@
       <c r="D495">
         <v>1</v>
       </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A496" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1</v>
+      </c>
+      <c r="C496" t="s">
+        <v>10</v>
+      </c>
+      <c r="D496">
+        <v>0</v>
+      </c>
+      <c r="E496">
+        <f>SUM(D496:D500)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A497" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1</v>
+      </c>
+      <c r="C497" t="s">
+        <v>51</v>
+      </c>
+      <c r="D497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A498" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1</v>
+      </c>
+      <c r="C498" t="s">
+        <v>16</v>
+      </c>
+      <c r="D498">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A499" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1</v>
+      </c>
+      <c r="C499" t="s">
+        <v>2</v>
+      </c>
+      <c r="D499">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A500" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1</v>
+      </c>
+      <c r="C500" t="s">
+        <v>78</v>
+      </c>
+      <c r="D500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A501" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B501" t="s">
+        <v>17</v>
+      </c>
+      <c r="C501" t="s">
+        <v>9</v>
+      </c>
+      <c r="D501">
+        <v>2</v>
+      </c>
+      <c r="E501">
+        <f>SUM(D501:D505)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A502" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B502" t="s">
+        <v>17</v>
+      </c>
+      <c r="C502" t="s">
+        <v>20</v>
+      </c>
+      <c r="D502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A503" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B503" t="s">
+        <v>17</v>
+      </c>
+      <c r="C503" t="s">
+        <v>47</v>
+      </c>
+      <c r="D503">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A504" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B504" t="s">
+        <v>17</v>
+      </c>
+      <c r="C504" t="s">
+        <v>28</v>
+      </c>
+      <c r="D504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A505" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B505" t="s">
+        <v>17</v>
+      </c>
+      <c r="C505" t="s">
+        <v>45</v>
+      </c>
+      <c r="D505">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A506" s="1"/>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A507" s="1"/>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A508" s="1"/>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A509" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F44C760E-2D14-452A-A309-9345A29AA07B}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A79A41C5-0FF7-444C-909D-300D415E6E1D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="92">
   <si>
     <t>Fecha</t>
   </si>
@@ -316,6 +316,12 @@
   <si>
     <t>Tomi</t>
   </si>
+  <si>
+    <t>Nico (amigo Bigo)</t>
+  </si>
+  <si>
+    <t>Kevin (amigo Bigo)</t>
+  </si>
 </sst>
 </file>
 
@@ -382,10 +388,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3023,7 +3025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:F525"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -10089,7 +10091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>46135</v>
       </c>
@@ -10103,7 +10105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>46135</v>
       </c>
@@ -10117,7 +10119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>46135</v>
       </c>
@@ -10131,7 +10133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>46135</v>
       </c>
@@ -10145,7 +10147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>46135</v>
       </c>
@@ -10163,7 +10165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>46135</v>
       </c>
@@ -10177,7 +10179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>46135</v>
       </c>
@@ -10191,7 +10193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>46135</v>
       </c>
@@ -10205,7 +10207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>46135</v>
       </c>
@@ -10219,17 +10221,307 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A506" s="1"/>
-    </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A507" s="1"/>
-    </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A508" s="1"/>
-    </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A509" s="1"/>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A506" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1</v>
+      </c>
+      <c r="C506" t="s">
+        <v>71</v>
+      </c>
+      <c r="D506">
+        <v>2</v>
+      </c>
+      <c r="E506">
+        <f>SUM(D506:D510)</f>
+        <v>5</v>
+      </c>
+      <c r="F506" s="1"/>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A507" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1</v>
+      </c>
+      <c r="C507" t="s">
+        <v>10</v>
+      </c>
+      <c r="D507">
+        <v>0</v>
+      </c>
+      <c r="F507" s="1"/>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A508" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1</v>
+      </c>
+      <c r="C508" t="s">
+        <v>30</v>
+      </c>
+      <c r="D508">
+        <v>0</v>
+      </c>
+      <c r="F508" s="1"/>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A509" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1</v>
+      </c>
+      <c r="C509" t="s">
+        <v>28</v>
+      </c>
+      <c r="D509">
+        <v>3</v>
+      </c>
+      <c r="F509" s="1"/>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A510" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1</v>
+      </c>
+      <c r="C510" t="s">
+        <v>48</v>
+      </c>
+      <c r="D510">
+        <v>0</v>
+      </c>
+      <c r="F510" s="1"/>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A511" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B511" t="s">
+        <v>17</v>
+      </c>
+      <c r="C511" t="s">
+        <v>16</v>
+      </c>
+      <c r="D511">
+        <v>1</v>
+      </c>
+      <c r="E511">
+        <f>SUM(D511:D515)</f>
+        <v>3</v>
+      </c>
+      <c r="F511" s="1"/>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A512" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B512" t="s">
+        <v>17</v>
+      </c>
+      <c r="C512" t="s">
+        <v>69</v>
+      </c>
+      <c r="D512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A513" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B513" t="s">
+        <v>17</v>
+      </c>
+      <c r="C513" t="s">
+        <v>70</v>
+      </c>
+      <c r="D513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A514" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B514" t="s">
+        <v>17</v>
+      </c>
+      <c r="C514" t="s">
+        <v>51</v>
+      </c>
+      <c r="D514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A515" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B515" t="s">
+        <v>17</v>
+      </c>
+      <c r="C515" t="s">
+        <v>47</v>
+      </c>
+      <c r="D515">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A516" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1</v>
+      </c>
+      <c r="C516" t="s">
+        <v>16</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516">
+        <f>SUM(D516:D520)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A517" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1</v>
+      </c>
+      <c r="C517" t="s">
+        <v>69</v>
+      </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A518" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1</v>
+      </c>
+      <c r="C518" t="s">
+        <v>90</v>
+      </c>
+      <c r="D518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A519" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1</v>
+      </c>
+      <c r="C519" t="s">
+        <v>91</v>
+      </c>
+      <c r="D519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A520" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1</v>
+      </c>
+      <c r="C520" t="s">
+        <v>75</v>
+      </c>
+      <c r="D520">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A521" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B521" t="s">
+        <v>17</v>
+      </c>
+      <c r="C521" t="s">
+        <v>51</v>
+      </c>
+      <c r="D521">
+        <v>5</v>
+      </c>
+      <c r="E521">
+        <f>SUM(D521:D525)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A522" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B522" t="s">
+        <v>17</v>
+      </c>
+      <c r="C522" t="s">
+        <v>20</v>
+      </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A523" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B523" t="s">
+        <v>17</v>
+      </c>
+      <c r="C523" t="s">
+        <v>48</v>
+      </c>
+      <c r="D523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A524" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B524" t="s">
+        <v>17</v>
+      </c>
+      <c r="C524" t="s">
+        <v>47</v>
+      </c>
+      <c r="D524">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A525" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B525" t="s">
+        <v>17</v>
+      </c>
+      <c r="C525" t="s">
+        <v>10</v>
+      </c>
+      <c r="D525">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="521" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A79A41C5-0FF7-444C-909D-300D415E6E1D}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097E0854-6445-40C1-BA53-F0DB6BA0DA4A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="94">
   <si>
     <t>Fecha</t>
   </si>
@@ -322,6 +322,12 @@
   <si>
     <t>Kevin (amigo Bigo)</t>
   </si>
+  <si>
+    <t>Diego (amigo Maxi)</t>
+  </si>
+  <si>
+    <t>Uruguayo (amigo de Facu)</t>
+  </si>
 </sst>
 </file>
 
@@ -388,6 +394,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3025,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F525"/>
+  <dimension ref="A1:F545"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -10521,6 +10531,302 @@
       </c>
       <c r="D525">
         <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A526" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1</v>
+      </c>
+      <c r="C526" t="s">
+        <v>69</v>
+      </c>
+      <c r="D526">
+        <v>2</v>
+      </c>
+      <c r="E526">
+        <f>SUM(D526:D530)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1</v>
+      </c>
+      <c r="C527" t="s">
+        <v>10</v>
+      </c>
+      <c r="D527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A528" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1</v>
+      </c>
+      <c r="C528" t="s">
+        <v>92</v>
+      </c>
+      <c r="D528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A529" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1</v>
+      </c>
+      <c r="C529" t="s">
+        <v>30</v>
+      </c>
+      <c r="D529">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A530" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1</v>
+      </c>
+      <c r="C530" t="s">
+        <v>48</v>
+      </c>
+      <c r="D530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A531" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B531" t="s">
+        <v>17</v>
+      </c>
+      <c r="C531" t="s">
+        <v>45</v>
+      </c>
+      <c r="D531">
+        <v>2</v>
+      </c>
+      <c r="E531">
+        <f>SUM(D531:D535)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A532" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B532" t="s">
+        <v>17</v>
+      </c>
+      <c r="C532" t="s">
+        <v>51</v>
+      </c>
+      <c r="D532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A533" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B533" t="s">
+        <v>17</v>
+      </c>
+      <c r="C533" t="s">
+        <v>28</v>
+      </c>
+      <c r="D533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A534" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B534" t="s">
+        <v>17</v>
+      </c>
+      <c r="C534" t="s">
+        <v>70</v>
+      </c>
+      <c r="D534">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A535" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B535" t="s">
+        <v>17</v>
+      </c>
+      <c r="C535" t="s">
+        <v>93</v>
+      </c>
+      <c r="D535">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A536" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1</v>
+      </c>
+      <c r="C536" t="s">
+        <v>10</v>
+      </c>
+      <c r="D536">
+        <v>0</v>
+      </c>
+      <c r="E536">
+        <f>SUM(D536:D540)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A537" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1</v>
+      </c>
+      <c r="C537" t="s">
+        <v>30</v>
+      </c>
+      <c r="D537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A538" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1</v>
+      </c>
+      <c r="C538" t="s">
+        <v>61</v>
+      </c>
+      <c r="D538">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A539" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1</v>
+      </c>
+      <c r="C539" t="s">
+        <v>48</v>
+      </c>
+      <c r="D539">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A540" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1</v>
+      </c>
+      <c r="C540" t="s">
+        <v>52</v>
+      </c>
+      <c r="D540">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A541" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B541" t="s">
+        <v>17</v>
+      </c>
+      <c r="C541" t="s">
+        <v>9</v>
+      </c>
+      <c r="D541">
+        <v>2</v>
+      </c>
+      <c r="E541">
+        <f>SUM(D541:D545)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A542" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B542" t="s">
+        <v>17</v>
+      </c>
+      <c r="C542" t="s">
+        <v>20</v>
+      </c>
+      <c r="D542">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A543" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B543" t="s">
+        <v>17</v>
+      </c>
+      <c r="C543" t="s">
+        <v>69</v>
+      </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A544" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B544" t="s">
+        <v>17</v>
+      </c>
+      <c r="C544" t="s">
+        <v>45</v>
+      </c>
+      <c r="D544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A545" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B545" t="s">
+        <v>17</v>
+      </c>
+      <c r="C545" t="s">
+        <v>51</v>
+      </c>
+      <c r="D545">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097E0854-6445-40C1-BA53-F0DB6BA0DA4A}"/>
+  <xr:revisionPtr revIDLastSave="614" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBE7655D-7B69-4276-9F2F-9E2F8A5D3103}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="94">
   <si>
     <t>Fecha</t>
   </si>
@@ -3035,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F545"/>
+  <dimension ref="A1:F556"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -10815,7 +10815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>46177</v>
       </c>
@@ -10828,6 +10828,157 @@
       <c r="D545">
         <v>1</v>
       </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A546" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1</v>
+      </c>
+      <c r="C546" t="s">
+        <v>10</v>
+      </c>
+      <c r="D546">
+        <v>0</v>
+      </c>
+      <c r="E546">
+        <f>SUM(D546:D550)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A547" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1</v>
+      </c>
+      <c r="C547" t="s">
+        <v>26</v>
+      </c>
+      <c r="D547">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A548" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1</v>
+      </c>
+      <c r="C548" t="s">
+        <v>48</v>
+      </c>
+      <c r="D548">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A549" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1</v>
+      </c>
+      <c r="C549" t="s">
+        <v>61</v>
+      </c>
+      <c r="D549">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A550" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1</v>
+      </c>
+      <c r="C550" t="s">
+        <v>20</v>
+      </c>
+      <c r="D550">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A551" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B551" t="s">
+        <v>17</v>
+      </c>
+      <c r="C551" t="s">
+        <v>9</v>
+      </c>
+      <c r="D551">
+        <v>2</v>
+      </c>
+      <c r="E551">
+        <f>SUM(D551:D555)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A552" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B552" t="s">
+        <v>17</v>
+      </c>
+      <c r="C552" t="s">
+        <v>71</v>
+      </c>
+      <c r="D552">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A553" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B553" t="s">
+        <v>17</v>
+      </c>
+      <c r="C553" t="s">
+        <v>30</v>
+      </c>
+      <c r="D553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A554" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B554" t="s">
+        <v>17</v>
+      </c>
+      <c r="C554" t="s">
+        <v>69</v>
+      </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A555" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B555" t="s">
+        <v>17</v>
+      </c>
+      <c r="C555" t="s">
+        <v>65</v>
+      </c>
+      <c r="D555">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A556" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/docs/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="614" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBE7655D-7B69-4276-9F2F-9E2F8A5D3103}"/>
+  <xr:revisionPtr revIDLastSave="641" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{918CF3BA-5165-49E1-8D32-E8B1AF138DF2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="94">
   <si>
     <t>Fecha</t>
   </si>
@@ -3035,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F556"/>
+  <dimension ref="A1:F566"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -10978,7 +10978,155 @@
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A556" s="1"/>
+      <c r="A556" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1</v>
+      </c>
+      <c r="C556" t="s">
+        <v>20</v>
+      </c>
+      <c r="D556">
+        <v>0</v>
+      </c>
+      <c r="E556">
+        <f>SUM(D556:D560)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A557" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1</v>
+      </c>
+      <c r="C557" t="s">
+        <v>9</v>
+      </c>
+      <c r="D557">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A558" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1</v>
+      </c>
+      <c r="C558" t="s">
+        <v>61</v>
+      </c>
+      <c r="D558">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A559" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1</v>
+      </c>
+      <c r="C559" t="s">
+        <v>51</v>
+      </c>
+      <c r="D559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A560" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1</v>
+      </c>
+      <c r="C560" t="s">
+        <v>45</v>
+      </c>
+      <c r="D560">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A561" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B561" t="s">
+        <v>17</v>
+      </c>
+      <c r="C561" t="s">
+        <v>10</v>
+      </c>
+      <c r="D561">
+        <v>0</v>
+      </c>
+      <c r="E561">
+        <f>SUM(D561:D565)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A562" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B562" t="s">
+        <v>17</v>
+      </c>
+      <c r="C562" t="s">
+        <v>48</v>
+      </c>
+      <c r="D562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A563" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B563" t="s">
+        <v>17</v>
+      </c>
+      <c r="C563" t="s">
+        <v>30</v>
+      </c>
+      <c r="D563">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A564" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B564" t="s">
+        <v>17</v>
+      </c>
+      <c r="C564" t="s">
+        <v>47</v>
+      </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A565" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B565" t="s">
+        <v>17</v>
+      </c>
+      <c r="C565" t="s">
+        <v>71</v>
+      </c>
+      <c r="D565">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A566" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D403" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
